--- a/syd.xlsx
+++ b/syd.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alanoud/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alanoud/Desktop/8.1D/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99689D2D-739D-FC43-9874-14474848B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1EF2191-1EA4-F04E-8001-2D814E7710F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16180" xr2:uid="{D662E734-3760-9447-AB59-F6EFCB681F18}"/>
   </bookViews>
